--- a/docs/standards/SJTDM_TAZ_Migration_Project_Control.xlsx
+++ b/docs/standards/SJTDM_TAZ_Migration_Project_Control.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kschellinger\SJTPO_Git\SJTDM_TAZ_Migration\docs\standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FABF13B-48D1-4D96-BEC7-F05CD3553E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9025B6-D93D-495D-88BB-DF702857C25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1830" windowWidth="29010" windowHeight="14370" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1500" yWindow="930" windowWidth="29010" windowHeight="14370" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="331">
   <si>
     <t>SJTDM TAZ Migration and Data Validation – Project Control Workbook</t>
   </si>
@@ -164,9 +164,6 @@
     <t>Task</t>
   </si>
   <si>
-    <t>Description</t>
-  </si>
-  <si>
     <t>Owner</t>
   </si>
   <si>
@@ -197,12 +194,6 @@
     <t>Project Foundation</t>
   </si>
   <si>
-    <t>Confirm repository structure</t>
-  </si>
-  <si>
-    <t>Confirm repo folder structure conforms to project needs and SJTPO standards.</t>
-  </si>
-  <si>
     <t>Kent</t>
   </si>
   <si>
@@ -221,12 +212,6 @@
     <t>T-002</t>
   </si>
   <si>
-    <t>Prepare project charter</t>
-  </si>
-  <si>
-    <t>Document purpose, scope, exclusions, assumptions, deliverables, and success criteria.</t>
-  </si>
-  <si>
     <t>Not Started</t>
   </si>
   <si>
@@ -242,12 +227,6 @@
     <t>Standards</t>
   </si>
   <si>
-    <t>Create file mirroring inventory</t>
-  </si>
-  <si>
-    <t>Track files that must exist both in Git and SJTPO GIS standard locations.</t>
-  </si>
-  <si>
     <t>File mirroring tracker</t>
   </si>
   <si>
@@ -263,12 +242,6 @@
     <t>Data Inventory</t>
   </si>
   <si>
-    <t>Inventory existing Access databases</t>
-  </si>
-  <si>
-    <t>List relevant Access databases created or extracted to date.</t>
-  </si>
-  <si>
     <t>Database inventory</t>
   </si>
   <si>
@@ -278,33 +251,12 @@
     <t>T-005</t>
   </si>
   <si>
-    <t>Inventory existing Excel workbooks</t>
-  </si>
-  <si>
-    <t>List source and generated Excel files created to date.</t>
-  </si>
-  <si>
-    <t>Workbook inventory</t>
-  </si>
-  <si>
-    <t>data/raw/Excel; data/intermediate/Inventories</t>
-  </si>
-  <si>
     <t>T-006</t>
   </si>
   <si>
-    <t>Inventory existing PDFs</t>
-  </si>
-  <si>
-    <t>List SJTDM, consultant, GIS standards, and relevant documentation PDFs.</t>
-  </si>
-  <si>
     <t>Medium</t>
   </si>
   <si>
-    <t>Document inventory</t>
-  </si>
-  <si>
     <t>docs/source_documents</t>
   </si>
   <si>
@@ -314,33 +266,12 @@
     <t>Model Discovery</t>
   </si>
   <si>
-    <t>Catalog Cube tables</t>
-  </si>
-  <si>
-    <t>Build table and field catalog from Cube Voyager code and model databases.</t>
-  </si>
-  <si>
-    <t>Cube table catalog</t>
-  </si>
-  <si>
     <t>data/intermediate/Inventories</t>
   </si>
   <si>
     <t>T-008</t>
   </si>
   <si>
-    <t>TAZ Validation</t>
-  </si>
-  <si>
-    <t>Define critical model variables</t>
-  </si>
-  <si>
-    <t>Classify fields used for trip generation, attraction, special generators, and area type.</t>
-  </si>
-  <si>
-    <t>Critical variable list</t>
-  </si>
-  <si>
     <t>docs/methodology</t>
   </si>
   <si>
@@ -350,30 +281,9 @@
     <t>Crosswalk</t>
   </si>
   <si>
-    <t>Document crosswalk method</t>
-  </si>
-  <si>
-    <t>Define 2011 TAZ, 2010 block, 2020 block, and 2020 TAZ relationship approach.</t>
-  </si>
-  <si>
-    <t>Crosswalk methodology</t>
-  </si>
-  <si>
     <t>T-010</t>
   </si>
   <si>
-    <t>QA/QC</t>
-  </si>
-  <si>
-    <t>Create exception review process</t>
-  </si>
-  <si>
-    <t>Define flag thresholds and manual review workflow.</t>
-  </si>
-  <si>
-    <t>QA/QC exception process</t>
-  </si>
-  <si>
     <t>FileName</t>
   </si>
   <si>
@@ -578,63 +488,12 @@
     <t>DI-005</t>
   </si>
   <si>
-    <t>2020 CBG-based TAZ layer</t>
-  </si>
-  <si>
-    <t>GIS</t>
-  </si>
-  <si>
-    <t>SJTPO / project</t>
-  </si>
-  <si>
-    <t>data/final</t>
-  </si>
-  <si>
-    <t>TAZ2020</t>
-  </si>
-  <si>
-    <t>New model zone system</t>
-  </si>
-  <si>
     <t>DI-006</t>
   </si>
   <si>
-    <t>Employment inputs</t>
-  </si>
-  <si>
-    <t>Excel/Access</t>
-  </si>
-  <si>
-    <t>data/raw/Excel</t>
-  </si>
-  <si>
-    <t>TAZ or block</t>
-  </si>
-  <si>
-    <t>TAZ / Block</t>
-  </si>
-  <si>
-    <t>Attractions</t>
-  </si>
-  <si>
     <t>DI-007</t>
   </si>
   <si>
-    <t>Special generators</t>
-  </si>
-  <si>
-    <t>SJTDM / project</t>
-  </si>
-  <si>
-    <t>GeneratorID</t>
-  </si>
-  <si>
-    <t>Point / TAZ</t>
-  </si>
-  <si>
-    <t>Trip generation adjustment</t>
-  </si>
-  <si>
     <t>StandardID</t>
   </si>
   <si>
@@ -680,60 +539,9 @@
     <t>metadata</t>
   </si>
   <si>
-    <t>SC-003</t>
-  </si>
-  <si>
-    <t>Document QA/QC procedures and exception review.</t>
-  </si>
-  <si>
-    <t>QA/QC register created; methodology pending.</t>
-  </si>
-  <si>
-    <t>QAQC_Register; docs/methodology</t>
-  </si>
-  <si>
-    <t>SC-004</t>
-  </si>
-  <si>
-    <t>Naming Conventions</t>
-  </si>
-  <si>
-    <t>Use consistent file, table, and layer naming conventions.</t>
-  </si>
-  <si>
-    <t>Initial convention: descriptive snake_case or SJTDM legacy names where required.</t>
-  </si>
-  <si>
-    <t>SC-005</t>
-  </si>
-  <si>
-    <t>Authoritative Storage</t>
-  </si>
-  <si>
-    <t>Mirror final GIS products to expected SJTPO GIS standard locations.</t>
-  </si>
-  <si>
-    <t>File mirroring tracker created; destination paths TBD.</t>
-  </si>
-  <si>
-    <t>File_Mirroring</t>
-  </si>
-  <si>
-    <t>SC-006</t>
-  </si>
-  <si>
     <t>Documentation</t>
   </si>
   <si>
-    <t>Maintain project documentation, source inventories, and processing notes.</t>
-  </si>
-  <si>
-    <t>Docs folder and README created.</t>
-  </si>
-  <si>
-    <t>docs; README.md</t>
-  </si>
-  <si>
     <t>IssueID</t>
   </si>
   <si>
@@ -879,6 +687,351 @@
   </si>
   <si>
     <t>Deferred</t>
+  </si>
+  <si>
+    <t>DI-008</t>
+  </si>
+  <si>
+    <t>SJTDM_Master_Tables_With_Fields.xlsx</t>
+  </si>
+  <si>
+    <t>Establish Git repository and folder structure</t>
+  </si>
+  <si>
+    <t>Complete project charter</t>
+  </si>
+  <si>
+    <t>Develop file mirroring inventory</t>
+  </si>
+  <si>
+    <t>Review SJTPO GIS Data Management requirements</t>
+  </si>
+  <si>
+    <t>Inventory Cube input files</t>
+  </si>
+  <si>
+    <t>Catalog SJTDM tables and fields</t>
+  </si>
+  <si>
+    <t>T-011</t>
+  </si>
+  <si>
+    <t>Identify TAZ-dependent tables</t>
+  </si>
+  <si>
+    <t>T-012</t>
+  </si>
+  <si>
+    <t>Data Lineage</t>
+  </si>
+  <si>
+    <t>Trace socioeconomic data sources</t>
+  </si>
+  <si>
+    <t>T-013</t>
+  </si>
+  <si>
+    <t>Trace employment data sources</t>
+  </si>
+  <si>
+    <t>T-014</t>
+  </si>
+  <si>
+    <t>Trace recreational trip data sources</t>
+  </si>
+  <si>
+    <t>T-015</t>
+  </si>
+  <si>
+    <t>TAZ Migration</t>
+  </si>
+  <si>
+    <t>Develop migration methodology</t>
+  </si>
+  <si>
+    <t>Develop crosswalk methodology</t>
+  </si>
+  <si>
+    <t>Define preservation metrics</t>
+  </si>
+  <si>
+    <t>Build validation procedures</t>
+  </si>
+  <si>
+    <t>Priority2</t>
+  </si>
+  <si>
+    <t>Inventory Cube scripts</t>
+  </si>
+  <si>
+    <t>Inventory all Cube Voyager scripts and identify execution order.</t>
+  </si>
+  <si>
+    <t>Cube Script Inventory</t>
+  </si>
+  <si>
+    <t>Foundation for model documentation.</t>
+  </si>
+  <si>
+    <t>Identify all model inputs referenced by Cube scripts.</t>
+  </si>
+  <si>
+    <t>Input File Inventory</t>
+  </si>
+  <si>
+    <t>Includes DBFs, CSVs, networks and lookup tables.</t>
+  </si>
+  <si>
+    <t>Validate existing table inventory and classify table purpose.</t>
+  </si>
+  <si>
+    <t>Table Catalog</t>
+  </si>
+  <si>
+    <t>Excel inventory already exists.</t>
+  </si>
+  <si>
+    <t>Determine which tables contain zonal data affecting model results.</t>
+  </si>
+  <si>
+    <t>TAZ Dependency Matrix</t>
+  </si>
+  <si>
+    <t>Critical migration task.</t>
+  </si>
+  <si>
+    <t>Document source-to-model workflow for population and households.</t>
+  </si>
+  <si>
+    <t>Data Lineage Documentation</t>
+  </si>
+  <si>
+    <t>Supports QA/QC.</t>
+  </si>
+  <si>
+    <t>Document source-to-model workflow for employment variables.</t>
+  </si>
+  <si>
+    <t>Employment Lineage Documentation</t>
+  </si>
+  <si>
+    <t>Supports trip attraction validation.</t>
+  </si>
+  <si>
+    <t>Document source-to-model workflow for recreational trip generation.</t>
+  </si>
+  <si>
+    <t>Recreation Lineage Documentation</t>
+  </si>
+  <si>
+    <t>Supports recreational TAZ migration.</t>
+  </si>
+  <si>
+    <t>Document methodology for transition from legacy TAZs to 2020 TAZs.</t>
+  </si>
+  <si>
+    <t>Migration Methodology</t>
+  </si>
+  <si>
+    <t>Document allocation and split/merge procedures.</t>
+  </si>
+  <si>
+    <t>Crosswalk Methodology</t>
+  </si>
+  <si>
+    <t>Required before validation.</t>
+  </si>
+  <si>
+    <t>Establish validation metrics for households, population and employment.</t>
+  </si>
+  <si>
+    <t>Validation Framework</t>
+  </si>
+  <si>
+    <t>docs/qa_reports</t>
+  </si>
+  <si>
+    <t>Replaces geometry-only QA/QC.</t>
+  </si>
+  <si>
+    <t>Develop queries and reports to evaluate preservation metrics.</t>
+  </si>
+  <si>
+    <t>Validation Procedures</t>
+  </si>
+  <si>
+    <t>Automated where possible.</t>
+  </si>
+  <si>
+    <t>SJTDM Inventory</t>
+  </si>
+  <si>
+    <t>TableName</t>
+  </si>
+  <si>
+    <t>Model System</t>
+  </si>
+  <si>
+    <t>Contains inventoried SJTDM tables and fields.</t>
+  </si>
+  <si>
+    <t>SJTDM_INPUTS_Data.accdb</t>
+  </si>
+  <si>
+    <t>SJTDM</t>
+  </si>
+  <si>
+    <t>Legacy</t>
+  </si>
+  <si>
+    <t>Multiple</t>
+  </si>
+  <si>
+    <t>Model Inputs</t>
+  </si>
+  <si>
+    <t>Primary source database for discovery.</t>
+  </si>
+  <si>
+    <t>Cube Voyager Scripts</t>
+  </si>
+  <si>
+    <t>Script Collection</t>
+  </si>
+  <si>
+    <t>data/raw/Cube</t>
+  </si>
+  <si>
+    <t>ScriptName</t>
+  </si>
+  <si>
+    <t>Model Execution</t>
+  </si>
+  <si>
+    <t>Inventory pending.</t>
+  </si>
+  <si>
+    <t>SJTDM Users Guide</t>
+  </si>
+  <si>
+    <t>SJTDM Documentation</t>
+  </si>
+  <si>
+    <t>Primary model documentation.</t>
+  </si>
+  <si>
+    <t>SJTDM_TAZ_Migration_Project_Control.xlsx</t>
+  </si>
+  <si>
+    <t>docs/standards</t>
+  </si>
+  <si>
+    <t>Master project tracker.</t>
+  </si>
+  <si>
+    <t>Table inventory workbook.</t>
+  </si>
+  <si>
+    <t>SJTPO Standard Location</t>
+  </si>
+  <si>
+    <t>Source database.</t>
+  </si>
+  <si>
+    <t>SJTDM Users Guide.pdf</t>
+  </si>
+  <si>
+    <t>Primary documentation.</t>
+  </si>
+  <si>
+    <t>SJTDM Tables</t>
+  </si>
+  <si>
+    <t>Table Usage</t>
+  </si>
+  <si>
+    <t>Documentation Review</t>
+  </si>
+  <si>
+    <t>Identify active model inputs</t>
+  </si>
+  <si>
+    <t>Distinguish active tables from legacy artifacts.</t>
+  </si>
+  <si>
+    <t>Pending Cube script review.</t>
+  </si>
+  <si>
+    <t>Key discovery task.</t>
+  </si>
+  <si>
+    <t>Socioeconomic Inputs</t>
+  </si>
+  <si>
+    <t>Population and Households</t>
+  </si>
+  <si>
+    <t>Source Trace</t>
+  </si>
+  <si>
+    <t>Complete lineage required</t>
+  </si>
+  <si>
+    <t>Source workflow not fully documented.</t>
+  </si>
+  <si>
+    <t>TAZ-dependent tables</t>
+  </si>
+  <si>
+    <t>Inventory</t>
+  </si>
+  <si>
+    <t>All TAZ tables identified</t>
+  </si>
+  <si>
+    <t>Unknown number of TAZ-sensitive tables.</t>
+  </si>
+  <si>
+    <t>Table Inventory</t>
+  </si>
+  <si>
+    <t>Critical project risk.</t>
+  </si>
+  <si>
+    <t>Q-006</t>
+  </si>
+  <si>
+    <t>TAZ Migration Variables</t>
+  </si>
+  <si>
+    <t>Preservation metrics established</t>
+  </si>
+  <si>
+    <t>Validation methodology not yet defined.</t>
+  </si>
+  <si>
+    <t>Required before migration QA/QC.</t>
+  </si>
+  <si>
+    <t>Column1</t>
+  </si>
+  <si>
+    <t>Column2</t>
+  </si>
+  <si>
+    <t>Column3</t>
+  </si>
+  <si>
+    <t>Column4</t>
+  </si>
+  <si>
+    <t>Column5</t>
+  </si>
+  <si>
+    <t>Core project objective.  First-pass review of recreational model TAZs completed. TAZs containing significant recreational land-use patterns and sub-census-block characteristics identified. Findings indicate that preservation of model-relevant land-use geography is more important than geometric similarity between legacy and proposed TAZ boundaries.</t>
+  </si>
+  <si>
+    <t>Recreational model screening methodology tested. Initial review confirms geometry-only comparisons are insufficient for evaluating migration quality. QA/QC framework shall evaluate preservation of socioeconomic and recreational model characteristics in addition to geometric correspondence.</t>
   </si>
 </sst>
 </file>
@@ -888,7 +1041,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -908,6 +1061,10 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -941,7 +1098,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -957,6 +1114,18 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -965,7 +1134,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="16">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1071,6 +1240,9 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" justifyLastLine="0" shrinkToFit="0" readingOrder="1"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1085,14 +1257,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TaskRegisterTable" displayName="TaskRegisterTable" ref="A1:M11">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TaskRegisterTable" displayName="TaskRegisterTable" ref="A1:M22">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="TaskID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Phase"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Task"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Description"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Priority"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Owner"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Priority"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Priority2"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="DueDate"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Status"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Dependency"/>
@@ -1106,7 +1278,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="FileMirroringTable" displayName="FileMirroringTable" ref="A1:J8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="FileMirroringTable" displayName="FileMirroringTable" ref="A1:J12">
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="FileName"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="FileType"/>
@@ -1124,10 +1296,10 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DataInventoryTable" displayName="DataInventoryTable" ref="A1:M8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="DataInventoryTable" displayName="DataInventoryTable" ref="A1:M10">
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="InventoryID"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="DatasetOrTable"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="DatasetOrTable" dataDxfId="15"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="SourceType"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0200-000004000000}" name="SourceSystem"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0200-000005000000}" name="ProjectRepoPath"/>
@@ -1145,8 +1317,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="StandardsComplianceTable" displayName="StandardsComplianceTable" ref="A1:H7">
-  <tableColumns count="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{00000000-000C-0000-FFFF-FFFF03000000}" name="StandardsComplianceTable" displayName="StandardsComplianceTable" ref="A1:M7">
+  <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0300-000001000000}" name="StandardID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0300-000002000000}" name="StandardArea"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0300-000003000000}" name="Requirement"/>
@@ -1155,6 +1327,11 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0300-000006000000}" name="Status"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0300-000007000000}" name="Owner"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0300-000008000000}" name="Notes"/>
+    <tableColumn id="9" xr3:uid="{3AA2AD53-E40A-4E36-83F1-935956DEB187}" name="Column1"/>
+    <tableColumn id="10" xr3:uid="{B7A98AE7-A851-4CC7-817C-0222C3B28434}" name="Column2"/>
+    <tableColumn id="11" xr3:uid="{7D7278AF-D2CF-414E-AA8D-988F7B8E6589}" name="Column3"/>
+    <tableColumn id="12" xr3:uid="{32E985E7-93B7-44A6-A529-3194CB48636B}" name="Column4"/>
+    <tableColumn id="13" xr3:uid="{6657693B-A825-4F41-8531-8398F4E15051}" name="Column5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1343,16 +1520,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
     </row>
     <row r="3" spans="1:8" ht="15">
       <c r="A3" s="2" t="s">
@@ -1387,17 +1564,17 @@
       <c r="D4" t="s">
         <v>10</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
       <c r="F4">
         <f>COUNTIFS(Task_Register!$H:$H,"&lt;&gt;Complete",Task_Register!$H:$H,"&lt;&gt;N/A",Task_Register!$A:$A,"&lt;&gt;")</f>
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
+      <c r="H4" s="3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -1411,17 +1588,17 @@
       <c r="D5" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F5">
         <f>COUNTIFS(Task_Register!$H:$H,"Blocked")</f>
         <v>0</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1435,17 +1612,17 @@
       <c r="D6" t="s">
         <v>21</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="3" t="s">
         <v>22</v>
       </c>
       <c r="F6">
         <f>COUNTIFS(File_Mirroring!$F:$F,"Yes")</f>
-        <v>5</v>
-      </c>
-      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" t="s">
+      <c r="H6" s="3" t="s">
         <v>23</v>
       </c>
     </row>
@@ -1453,27 +1630,25 @@
       <c r="A7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="4">
-        <v>46181</v>
-      </c>
+      <c r="B7" s="3"/>
       <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F7">
         <f>COUNTIFS(File_Mirroring!$F:$F,"Yes",File_Mirroring!$H:$H,"&lt;&gt;Mirrored",File_Mirroring!$A:$A,"&lt;&gt;")</f>
-        <v>5</v>
-      </c>
-      <c r="G7" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H7" t="s">
+      <c r="H7" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15">
+    <row r="8" spans="1:8" ht="29.25">
       <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
@@ -1483,17 +1658,17 @@
       <c r="D8" t="s">
         <v>30</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="3" t="s">
         <v>31</v>
       </c>
       <c r="F8">
         <f>COUNTIFS(QAQC_Register!$H:$H,"&lt;&gt;Complete",QAQC_Register!$H:$H,"&lt;&gt;N/A",QAQC_Register!$A:$A,"&lt;&gt;")</f>
         <v>6</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H8" t="s">
+      <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1507,17 +1682,17 @@
       <c r="D9" t="s">
         <v>35</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="3" t="s">
         <v>36</v>
       </c>
       <c r="F9">
         <f>COUNTIFS(Standards_Compliance!$F:$F,"&lt;&gt;Complete",Standards_Compliance!$F:$F,"&lt;&gt;N/A",Standards_Compliance!$A:$A,"&lt;&gt;")</f>
         <v>7</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G9" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H9" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1531,7 +1706,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:M200"/>
+  <dimension ref="A1:M211"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="3" width="18" customWidth="1"/>
@@ -1541,453 +1716,711 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="15">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="5" t="s">
-        <v>42</v>
-      </c>
       <c r="F1" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="G1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>48</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>49</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="28.5">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:13" ht="42.75">
+      <c r="A2" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>52</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>55</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>56</v>
+        <v>214</v>
       </c>
       <c r="I2" s="3"/>
       <c r="J2" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="L2" s="3"/>
       <c r="M2" s="3" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="42.75">
-      <c r="A3" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="28.5">
+      <c r="A3" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>54</v>
-      </c>
       <c r="F3" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" ht="28.5">
-      <c r="A4" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>68</v>
+      <c r="A4" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" s="3" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="28.5">
-      <c r="A5" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="42.75">
+      <c r="A5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>52</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" ht="28.5">
-      <c r="A6" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>80</v>
+      <c r="A6" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>241</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I6" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>49</v>
+      </c>
       <c r="J6" s="3" t="s">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
+      <c r="M6" s="3" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="7" spans="1:13" ht="28.5">
-      <c r="A7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>85</v>
+      <c r="A7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>244</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="3"/>
+        <v>57</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>69</v>
+      </c>
       <c r="J7" s="3" t="s">
-        <v>87</v>
+        <v>245</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
       <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
+      <c r="M7" s="3" t="s">
+        <v>246</v>
+      </c>
     </row>
     <row r="8" spans="1:13" ht="28.5">
-      <c r="A8" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>92</v>
+      <c r="A8" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>247</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>93</v>
+        <v>248</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
+      <c r="M8" s="3" t="s">
+        <v>249</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="28.5">
-      <c r="A9" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>98</v>
+      <c r="A9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G9" s="4"/>
       <c r="H9" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" ht="28.5">
-      <c r="A10" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>104</v>
+      <c r="M9" s="3" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="42.75">
+      <c r="A10" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>253</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G10" s="4"/>
       <c r="H10" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>105</v>
+        <v>254</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
+      <c r="M10" s="3" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="11" spans="1:13" ht="28.5">
-      <c r="A11" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>109</v>
+      <c r="A11" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>256</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="G11" s="4"/>
       <c r="H11" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>95</v>
+        <v>76</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>110</v>
+        <v>257</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="G13" s="6"/>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="G14" s="6"/>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="G15" s="6"/>
-    </row>
-    <row r="16" spans="1:13">
-      <c r="G16" s="6"/>
-    </row>
-    <row r="17" spans="7:7">
-      <c r="G17" s="6"/>
-    </row>
-    <row r="18" spans="7:7">
-      <c r="G18" s="6"/>
-    </row>
-    <row r="19" spans="7:7">
-      <c r="G19" s="6"/>
-    </row>
-    <row r="20" spans="7:7">
-      <c r="G20" s="6"/>
-    </row>
-    <row r="21" spans="7:7">
-      <c r="G21" s="6"/>
-    </row>
-    <row r="22" spans="7:7">
-      <c r="G22" s="6"/>
-    </row>
-    <row r="23" spans="7:7">
+      <c r="M11" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="28.5">
+      <c r="A12" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G12" s="4"/>
+      <c r="H12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L12" s="3"/>
+      <c r="M12" s="3" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="185.25">
+      <c r="A13" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G13" s="4"/>
+      <c r="H13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L13" s="3"/>
+      <c r="M13" s="3" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="142.5">
+      <c r="A14" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L14" s="3"/>
+      <c r="M14" s="3" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="28.5">
+      <c r="A15" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G15" s="4"/>
+      <c r="H15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L15" s="3"/>
+      <c r="M15" s="3" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="28.5">
+      <c r="A16" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="4"/>
+      <c r="H16" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="L16" s="3"/>
+      <c r="M16" s="3" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="3"/>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3"/>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="3"/>
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="3"/>
+      <c r="F21" s="3"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="3"/>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="K21" s="3"/>
+      <c r="L21" s="3"/>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="3"/>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="1:13">
       <c r="G23" s="6"/>
     </row>
-    <row r="24" spans="7:7">
+    <row r="24" spans="1:13">
       <c r="G24" s="6"/>
     </row>
-    <row r="25" spans="7:7">
+    <row r="25" spans="1:13">
       <c r="G25" s="6"/>
     </row>
-    <row r="26" spans="7:7">
+    <row r="26" spans="1:13">
       <c r="G26" s="6"/>
     </row>
-    <row r="27" spans="7:7">
+    <row r="27" spans="1:13">
       <c r="G27" s="6"/>
     </row>
-    <row r="28" spans="7:7">
+    <row r="28" spans="1:13">
       <c r="G28" s="6"/>
     </row>
-    <row r="29" spans="7:7">
+    <row r="29" spans="1:13">
       <c r="G29" s="6"/>
     </row>
-    <row r="30" spans="7:7">
+    <row r="30" spans="1:13">
       <c r="G30" s="6"/>
     </row>
-    <row r="31" spans="7:7">
+    <row r="31" spans="1:13">
       <c r="G31" s="6"/>
     </row>
-    <row r="32" spans="7:7">
+    <row r="32" spans="1:13">
       <c r="G32" s="6"/>
     </row>
     <row r="33" spans="7:7">
@@ -2494,8 +2927,41 @@
     <row r="200" spans="7:7">
       <c r="G200" s="6"/>
     </row>
+    <row r="201" spans="7:7">
+      <c r="G201" s="6"/>
+    </row>
+    <row r="202" spans="7:7">
+      <c r="G202" s="6"/>
+    </row>
+    <row r="203" spans="7:7">
+      <c r="G203" s="6"/>
+    </row>
+    <row r="204" spans="7:7">
+      <c r="G204" s="6"/>
+    </row>
+    <row r="205" spans="7:7">
+      <c r="G205" s="6"/>
+    </row>
+    <row r="206" spans="7:7">
+      <c r="G206" s="6"/>
+    </row>
+    <row r="207" spans="7:7">
+      <c r="G207" s="6"/>
+    </row>
+    <row r="208" spans="7:7">
+      <c r="G208" s="6"/>
+    </row>
+    <row r="209" spans="7:7">
+      <c r="G209" s="6"/>
+    </row>
+    <row r="210" spans="7:7">
+      <c r="G210" s="6"/>
+    </row>
+    <row r="211" spans="7:7">
+      <c r="G211" s="6"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="H2:H200">
+  <conditionalFormatting sqref="H2:H211">
     <cfRule type="expression" dxfId="14" priority="1">
       <formula>$H2="Blocked"</formula>
     </cfRule>
@@ -2517,13 +2983,13 @@
           <x14:formula1>
             <xm:f>Lookup_Lists!$B$2:$B$5</xm:f>
           </x14:formula1>
-          <xm:sqref>F2:F200</xm:sqref>
+          <xm:sqref>F2:F211</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>Lookup_Lists!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>H2:H200</xm:sqref>
+          <xm:sqref>H2:H211</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2544,31 +3010,31 @@
   <sheetData>
     <row r="1" spans="1:10" ht="15">
       <c r="A1" s="5" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="J1" s="5" t="s">
         <v>6</v>
@@ -2576,257 +3042,321 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G2" s="4"/>
       <c r="H2" s="3" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>124</v>
+        <v>94</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="28.5">
       <c r="A4" s="3" t="s">
-        <v>125</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="42.75">
       <c r="A5" s="3" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>131</v>
+        <v>101</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>132</v>
+        <v>102</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G5" s="4"/>
       <c r="H5" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="28.5">
       <c r="A6" s="3" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G6" s="4"/>
       <c r="H6" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="28.5">
       <c r="A7" s="3" t="s">
-        <v>138</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G7" s="4"/>
       <c r="H7" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="28.5">
       <c r="A8" s="3" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>126</v>
+        <v>96</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="G8" s="4"/>
       <c r="H8" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="28.5">
+      <c r="A9" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="4"/>
+      <c r="H9" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="28.5">
+      <c r="A10" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="4"/>
+      <c r="H10" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="28.5">
+      <c r="A11" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="4"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3" t="s">
+        <v>68</v>
+      </c>
       <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
+      <c r="E11" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G11" s="4"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="H11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="28.5">
+      <c r="A12" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
+      <c r="E12" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>98</v>
+      </c>
       <c r="G12" s="4"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="H12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="3"/>
@@ -5131,7 +5661,9 @@
   <dimension ref="A1:M200"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="9" width="20" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="1"/>
+    <col min="2" max="2" width="35.5" style="8" customWidth="1"/>
+    <col min="3" max="9" width="20" customWidth="1"/>
     <col min="10" max="10" width="34" customWidth="1"/>
     <col min="11" max="12" width="20" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
@@ -5139,40 +5671,40 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15">
       <c r="A1" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>144</v>
+        <v>113</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>114</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>6</v>
@@ -5180,295 +5712,318 @@
     </row>
     <row r="2" spans="1:13" ht="28.5">
       <c r="A2" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>122</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>135</v>
+        <v>105</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" ht="28.5">
       <c r="A3" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>158</v>
+        <v>127</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>128</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>165</v>
+        <v>134</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>135</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>144</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" ht="28.5">
       <c r="A6" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>179</v>
+        <v>148</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>217</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>180</v>
+        <v>96</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>181</v>
+        <v>274</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>176</v>
+        <v>275</v>
+      </c>
+      <c r="H6" s="3">
+        <v>2026</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>154</v>
+        <v>276</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>62</v>
+        <v>214</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>277</v>
+      </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>186</v>
+        <v>149</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>278</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>127</v>
+        <v>279</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3" t="s">
-        <v>189</v>
+        <v>131</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>190</v>
+        <v>281</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>191</v>
+        <v>282</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M7" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>283</v>
+      </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>193</v>
+        <v>150</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>284</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>187</v>
+        <v>285</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>194</v>
+        <v>279</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>127</v>
-      </c>
+        <v>286</v>
+      </c>
+      <c r="F8" s="3"/>
       <c r="G8" s="3" t="s">
-        <v>195</v>
+        <v>287</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>127</v>
+        <v>280</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>196</v>
+        <v>276</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>197</v>
+        <v>288</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
+        <v>51</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="28.5">
+      <c r="A9" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>290</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+      <c r="G9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2010</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M9" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
@@ -5483,7 +6038,6 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
@@ -5498,7 +6052,6 @@
     </row>
     <row r="12" spans="1:13">
       <c r="A12" s="3"/>
-      <c r="B12" s="3"/>
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
@@ -5513,7 +6066,6 @@
     </row>
     <row r="13" spans="1:13">
       <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
       <c r="C13" s="3"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
@@ -5528,7 +6080,6 @@
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
       <c r="C14" s="3"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -5543,7 +6094,6 @@
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
       <c r="C15" s="3"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -5558,7 +6108,6 @@
     </row>
     <row r="16" spans="1:13">
       <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -5573,7 +6122,6 @@
     </row>
     <row r="17" spans="1:13">
       <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
@@ -5588,7 +6136,6 @@
     </row>
     <row r="18" spans="1:13">
       <c r="A18" s="3"/>
-      <c r="B18" s="3"/>
       <c r="C18" s="3"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -5603,7 +6150,6 @@
     </row>
     <row r="19" spans="1:13">
       <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
@@ -5618,7 +6164,6 @@
     </row>
     <row r="20" spans="1:13">
       <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -5633,7 +6178,6 @@
     </row>
     <row r="21" spans="1:13">
       <c r="A21" s="3"/>
-      <c r="B21" s="3"/>
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
@@ -5648,7 +6192,6 @@
     </row>
     <row r="22" spans="1:13">
       <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -5663,7 +6206,6 @@
     </row>
     <row r="23" spans="1:13">
       <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -5678,7 +6220,6 @@
     </row>
     <row r="24" spans="1:13">
       <c r="A24" s="3"/>
-      <c r="B24" s="3"/>
       <c r="C24" s="3"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
@@ -5693,7 +6234,6 @@
     </row>
     <row r="25" spans="1:13">
       <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -5708,7 +6248,6 @@
     </row>
     <row r="26" spans="1:13">
       <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
       <c r="C26" s="3"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
@@ -5723,7 +6262,6 @@
     </row>
     <row r="27" spans="1:13">
       <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -5738,7 +6276,6 @@
     </row>
     <row r="28" spans="1:13">
       <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
       <c r="C28" s="3"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
@@ -5753,7 +6290,6 @@
     </row>
     <row r="29" spans="1:13">
       <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -5768,7 +6304,6 @@
     </row>
     <row r="30" spans="1:13">
       <c r="A30" s="3"/>
-      <c r="B30" s="3"/>
       <c r="C30" s="3"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
@@ -5783,7 +6318,6 @@
     </row>
     <row r="31" spans="1:13">
       <c r="A31" s="3"/>
-      <c r="B31" s="3"/>
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -5798,7 +6332,6 @@
     </row>
     <row r="32" spans="1:13">
       <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
       <c r="C32" s="3"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -5813,7 +6346,6 @@
     </row>
     <row r="33" spans="1:13">
       <c r="A33" s="3"/>
-      <c r="B33" s="3"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -5828,7 +6360,6 @@
     </row>
     <row r="34" spans="1:13">
       <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -5843,7 +6374,6 @@
     </row>
     <row r="35" spans="1:13">
       <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -5858,7 +6388,6 @@
     </row>
     <row r="36" spans="1:13">
       <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -5873,7 +6402,6 @@
     </row>
     <row r="37" spans="1:13">
       <c r="A37" s="3"/>
-      <c r="B37" s="3"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -5888,7 +6416,6 @@
     </row>
     <row r="38" spans="1:13">
       <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -5903,7 +6430,6 @@
     </row>
     <row r="39" spans="1:13">
       <c r="A39" s="3"/>
-      <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
@@ -5918,7 +6444,6 @@
     </row>
     <row r="40" spans="1:13">
       <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
@@ -5933,7 +6458,6 @@
     </row>
     <row r="41" spans="1:13">
       <c r="A41" s="3"/>
-      <c r="B41" s="3"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
@@ -5948,7 +6472,6 @@
     </row>
     <row r="42" spans="1:13">
       <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
@@ -5963,7 +6486,6 @@
     </row>
     <row r="43" spans="1:13">
       <c r="A43" s="3"/>
-      <c r="B43" s="3"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
@@ -5978,7 +6500,6 @@
     </row>
     <row r="44" spans="1:13">
       <c r="A44" s="3"/>
-      <c r="B44" s="3"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
@@ -5993,7 +6514,6 @@
     </row>
     <row r="45" spans="1:13">
       <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
@@ -6008,7 +6528,6 @@
     </row>
     <row r="46" spans="1:13">
       <c r="A46" s="3"/>
-      <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
@@ -6023,7 +6542,6 @@
     </row>
     <row r="47" spans="1:13">
       <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
@@ -6038,7 +6556,6 @@
     </row>
     <row r="48" spans="1:13">
       <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
@@ -6053,7 +6570,6 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
@@ -6068,7 +6584,6 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="3"/>
-      <c r="B50" s="3"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
@@ -6083,7 +6598,6 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
@@ -6098,7 +6612,6 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="3"/>
-      <c r="B52" s="3"/>
       <c r="C52" s="3"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -6113,7 +6626,6 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -6128,7 +6640,6 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="3"/>
-      <c r="B54" s="3"/>
       <c r="C54" s="3"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -6143,7 +6654,6 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
@@ -6158,7 +6668,6 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
       <c r="C56" s="3"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
@@ -6173,7 +6682,6 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
@@ -6188,7 +6696,6 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
       <c r="C58" s="3"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
@@ -6203,7 +6710,6 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
       <c r="C59" s="3"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
@@ -6218,7 +6724,6 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="3"/>
-      <c r="B60" s="3"/>
       <c r="C60" s="3"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
@@ -6233,7 +6738,6 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="3"/>
-      <c r="B61" s="3"/>
       <c r="C61" s="3"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
@@ -6248,7 +6752,6 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="3"/>
-      <c r="B62" s="3"/>
       <c r="C62" s="3"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
@@ -6263,7 +6766,6 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
       <c r="C63" s="3"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -6278,7 +6780,6 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
       <c r="C64" s="3"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
@@ -6293,7 +6794,6 @@
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
@@ -6308,7 +6808,6 @@
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="3"/>
-      <c r="B66" s="3"/>
       <c r="C66" s="3"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
@@ -6323,7 +6822,6 @@
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
       <c r="C67" s="3"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
@@ -6338,7 +6836,6 @@
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
       <c r="C68" s="3"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
@@ -6353,7 +6850,6 @@
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
       <c r="C69" s="3"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
@@ -6368,7 +6864,6 @@
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="3"/>
-      <c r="B70" s="3"/>
       <c r="C70" s="3"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
@@ -6383,7 +6878,6 @@
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="3"/>
-      <c r="B71" s="3"/>
       <c r="C71" s="3"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
@@ -6398,7 +6892,6 @@
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="3"/>
-      <c r="B72" s="3"/>
       <c r="C72" s="3"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
@@ -6413,7 +6906,6 @@
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="3"/>
-      <c r="B73" s="3"/>
       <c r="C73" s="3"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
@@ -6428,7 +6920,6 @@
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
       <c r="C74" s="3"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
@@ -6443,7 +6934,6 @@
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="3"/>
-      <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
@@ -6458,7 +6948,6 @@
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
       <c r="C76" s="3"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
@@ -6473,7 +6962,6 @@
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
       <c r="C77" s="3"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
@@ -6488,7 +6976,6 @@
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="3"/>
-      <c r="B78" s="3"/>
       <c r="C78" s="3"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
@@ -6503,7 +6990,6 @@
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="3"/>
-      <c r="B79" s="3"/>
       <c r="C79" s="3"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
@@ -6518,7 +7004,6 @@
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
       <c r="C80" s="3"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
@@ -6533,7 +7018,6 @@
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
       <c r="C81" s="3"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
@@ -6548,7 +7032,6 @@
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="3"/>
-      <c r="B82" s="3"/>
       <c r="C82" s="3"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
@@ -6563,7 +7046,6 @@
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="3"/>
-      <c r="B83" s="3"/>
       <c r="C83" s="3"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
@@ -6578,7 +7060,6 @@
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
       <c r="C84" s="3"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
@@ -6593,7 +7074,6 @@
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
       <c r="C85" s="3"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
@@ -6608,7 +7088,6 @@
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
       <c r="C86" s="3"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
@@ -6623,7 +7102,6 @@
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="3"/>
-      <c r="B87" s="3"/>
       <c r="C87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
@@ -6638,7 +7116,6 @@
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="3"/>
-      <c r="B88" s="3"/>
       <c r="C88" s="3"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
@@ -6653,7 +7130,6 @@
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="3"/>
-      <c r="B89" s="3"/>
       <c r="C89" s="3"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
@@ -6668,7 +7144,6 @@
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="3"/>
-      <c r="B90" s="3"/>
       <c r="C90" s="3"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
@@ -6683,7 +7158,6 @@
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="3"/>
-      <c r="B91" s="3"/>
       <c r="C91" s="3"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
@@ -6698,7 +7172,6 @@
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="3"/>
-      <c r="B92" s="3"/>
       <c r="C92" s="3"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
@@ -6713,7 +7186,6 @@
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="3"/>
-      <c r="B93" s="3"/>
       <c r="C93" s="3"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
@@ -6728,7 +7200,6 @@
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="3"/>
-      <c r="B94" s="3"/>
       <c r="C94" s="3"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
@@ -6743,7 +7214,6 @@
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="3"/>
-      <c r="B95" s="3"/>
       <c r="C95" s="3"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
@@ -6758,7 +7228,6 @@
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="3"/>
-      <c r="B96" s="3"/>
       <c r="C96" s="3"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
@@ -6773,7 +7242,6 @@
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="3"/>
-      <c r="B97" s="3"/>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
@@ -6788,7 +7256,6 @@
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
       <c r="C98" s="3"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
@@ -6803,7 +7270,6 @@
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="3"/>
-      <c r="B99" s="3"/>
       <c r="C99" s="3"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -6818,7 +7284,6 @@
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="3"/>
-      <c r="B100" s="3"/>
       <c r="C100" s="3"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -6833,7 +7298,6 @@
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="3"/>
-      <c r="B101" s="3"/>
       <c r="C101" s="3"/>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
@@ -6848,7 +7312,6 @@
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="3"/>
-      <c r="B102" s="3"/>
       <c r="C102" s="3"/>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
@@ -6863,7 +7326,6 @@
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="3"/>
-      <c r="B103" s="3"/>
       <c r="C103" s="3"/>
       <c r="D103" s="3"/>
       <c r="E103" s="3"/>
@@ -6878,7 +7340,6 @@
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="3"/>
-      <c r="B104" s="3"/>
       <c r="C104" s="3"/>
       <c r="D104" s="3"/>
       <c r="E104" s="3"/>
@@ -6893,7 +7354,6 @@
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="3"/>
-      <c r="B105" s="3"/>
       <c r="C105" s="3"/>
       <c r="D105" s="3"/>
       <c r="E105" s="3"/>
@@ -6908,7 +7368,6 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="3"/>
-      <c r="B106" s="3"/>
       <c r="C106" s="3"/>
       <c r="D106" s="3"/>
       <c r="E106" s="3"/>
@@ -6923,7 +7382,6 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="3"/>
-      <c r="B107" s="3"/>
       <c r="C107" s="3"/>
       <c r="D107" s="3"/>
       <c r="E107" s="3"/>
@@ -6938,7 +7396,6 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="3"/>
-      <c r="B108" s="3"/>
       <c r="C108" s="3"/>
       <c r="D108" s="3"/>
       <c r="E108" s="3"/>
@@ -6953,7 +7410,6 @@
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="3"/>
-      <c r="B109" s="3"/>
       <c r="C109" s="3"/>
       <c r="D109" s="3"/>
       <c r="E109" s="3"/>
@@ -6968,7 +7424,6 @@
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
       <c r="C110" s="3"/>
       <c r="D110" s="3"/>
       <c r="E110" s="3"/>
@@ -6983,7 +7438,6 @@
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="3"/>
-      <c r="B111" s="3"/>
       <c r="C111" s="3"/>
       <c r="D111" s="3"/>
       <c r="E111" s="3"/>
@@ -6998,7 +7452,6 @@
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="3"/>
-      <c r="B112" s="3"/>
       <c r="C112" s="3"/>
       <c r="D112" s="3"/>
       <c r="E112" s="3"/>
@@ -7013,7 +7466,6 @@
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="3"/>
-      <c r="B113" s="3"/>
       <c r="C113" s="3"/>
       <c r="D113" s="3"/>
       <c r="E113" s="3"/>
@@ -7028,7 +7480,6 @@
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="3"/>
-      <c r="B114" s="3"/>
       <c r="C114" s="3"/>
       <c r="D114" s="3"/>
       <c r="E114" s="3"/>
@@ -7043,7 +7494,6 @@
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="3"/>
-      <c r="B115" s="3"/>
       <c r="C115" s="3"/>
       <c r="D115" s="3"/>
       <c r="E115" s="3"/>
@@ -7058,7 +7508,6 @@
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="3"/>
-      <c r="B116" s="3"/>
       <c r="C116" s="3"/>
       <c r="D116" s="3"/>
       <c r="E116" s="3"/>
@@ -7073,7 +7522,6 @@
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="3"/>
-      <c r="B117" s="3"/>
       <c r="C117" s="3"/>
       <c r="D117" s="3"/>
       <c r="E117" s="3"/>
@@ -7088,7 +7536,6 @@
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
       <c r="C118" s="3"/>
       <c r="D118" s="3"/>
       <c r="E118" s="3"/>
@@ -7103,7 +7550,6 @@
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="3"/>
-      <c r="B119" s="3"/>
       <c r="C119" s="3"/>
       <c r="D119" s="3"/>
       <c r="E119" s="3"/>
@@ -7118,7 +7564,6 @@
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="3"/>
-      <c r="B120" s="3"/>
       <c r="C120" s="3"/>
       <c r="D120" s="3"/>
       <c r="E120" s="3"/>
@@ -7133,7 +7578,6 @@
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="3"/>
-      <c r="B121" s="3"/>
       <c r="C121" s="3"/>
       <c r="D121" s="3"/>
       <c r="E121" s="3"/>
@@ -7148,7 +7592,6 @@
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="3"/>
-      <c r="B122" s="3"/>
       <c r="C122" s="3"/>
       <c r="D122" s="3"/>
       <c r="E122" s="3"/>
@@ -7163,7 +7606,6 @@
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="3"/>
-      <c r="B123" s="3"/>
       <c r="C123" s="3"/>
       <c r="D123" s="3"/>
       <c r="E123" s="3"/>
@@ -7178,7 +7620,6 @@
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="3"/>
-      <c r="B124" s="3"/>
       <c r="C124" s="3"/>
       <c r="D124" s="3"/>
       <c r="E124" s="3"/>
@@ -7193,7 +7634,6 @@
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="3"/>
-      <c r="B125" s="3"/>
       <c r="C125" s="3"/>
       <c r="D125" s="3"/>
       <c r="E125" s="3"/>
@@ -7208,7 +7648,6 @@
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="3"/>
-      <c r="B126" s="3"/>
       <c r="C126" s="3"/>
       <c r="D126" s="3"/>
       <c r="E126" s="3"/>
@@ -7223,7 +7662,6 @@
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="3"/>
-      <c r="B127" s="3"/>
       <c r="C127" s="3"/>
       <c r="D127" s="3"/>
       <c r="E127" s="3"/>
@@ -7238,7 +7676,6 @@
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
       <c r="C128" s="3"/>
       <c r="D128" s="3"/>
       <c r="E128" s="3"/>
@@ -7253,7 +7690,6 @@
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="3"/>
-      <c r="B129" s="3"/>
       <c r="C129" s="3"/>
       <c r="D129" s="3"/>
       <c r="E129" s="3"/>
@@ -7268,7 +7704,6 @@
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="3"/>
-      <c r="B130" s="3"/>
       <c r="C130" s="3"/>
       <c r="D130" s="3"/>
       <c r="E130" s="3"/>
@@ -7283,7 +7718,6 @@
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
       <c r="C131" s="3"/>
       <c r="D131" s="3"/>
       <c r="E131" s="3"/>
@@ -7298,7 +7732,6 @@
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="3"/>
-      <c r="B132" s="3"/>
       <c r="C132" s="3"/>
       <c r="D132" s="3"/>
       <c r="E132" s="3"/>
@@ -7313,7 +7746,6 @@
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
       <c r="C133" s="3"/>
       <c r="D133" s="3"/>
       <c r="E133" s="3"/>
@@ -7328,7 +7760,6 @@
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="3"/>
-      <c r="B134" s="3"/>
       <c r="C134" s="3"/>
       <c r="D134" s="3"/>
       <c r="E134" s="3"/>
@@ -7343,7 +7774,6 @@
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="3"/>
-      <c r="B135" s="3"/>
       <c r="C135" s="3"/>
       <c r="D135" s="3"/>
       <c r="E135" s="3"/>
@@ -7358,7 +7788,6 @@
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="3"/>
-      <c r="B136" s="3"/>
       <c r="C136" s="3"/>
       <c r="D136" s="3"/>
       <c r="E136" s="3"/>
@@ -7373,7 +7802,6 @@
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="3"/>
-      <c r="B137" s="3"/>
       <c r="C137" s="3"/>
       <c r="D137" s="3"/>
       <c r="E137" s="3"/>
@@ -7388,7 +7816,6 @@
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="3"/>
-      <c r="B138" s="3"/>
       <c r="C138" s="3"/>
       <c r="D138" s="3"/>
       <c r="E138" s="3"/>
@@ -7403,7 +7830,6 @@
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="3"/>
-      <c r="B139" s="3"/>
       <c r="C139" s="3"/>
       <c r="D139" s="3"/>
       <c r="E139" s="3"/>
@@ -7418,7 +7844,6 @@
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="3"/>
-      <c r="B140" s="3"/>
       <c r="C140" s="3"/>
       <c r="D140" s="3"/>
       <c r="E140" s="3"/>
@@ -7433,7 +7858,6 @@
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="3"/>
-      <c r="B141" s="3"/>
       <c r="C141" s="3"/>
       <c r="D141" s="3"/>
       <c r="E141" s="3"/>
@@ -7448,7 +7872,6 @@
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="3"/>
-      <c r="B142" s="3"/>
       <c r="C142" s="3"/>
       <c r="D142" s="3"/>
       <c r="E142" s="3"/>
@@ -7463,7 +7886,6 @@
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="3"/>
-      <c r="B143" s="3"/>
       <c r="C143" s="3"/>
       <c r="D143" s="3"/>
       <c r="E143" s="3"/>
@@ -7478,7 +7900,6 @@
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="3"/>
-      <c r="B144" s="3"/>
       <c r="C144" s="3"/>
       <c r="D144" s="3"/>
       <c r="E144" s="3"/>
@@ -7493,7 +7914,6 @@
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="3"/>
-      <c r="B145" s="3"/>
       <c r="C145" s="3"/>
       <c r="D145" s="3"/>
       <c r="E145" s="3"/>
@@ -7508,7 +7928,6 @@
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="3"/>
-      <c r="B146" s="3"/>
       <c r="C146" s="3"/>
       <c r="D146" s="3"/>
       <c r="E146" s="3"/>
@@ -7523,7 +7942,6 @@
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="3"/>
-      <c r="B147" s="3"/>
       <c r="C147" s="3"/>
       <c r="D147" s="3"/>
       <c r="E147" s="3"/>
@@ -7538,7 +7956,6 @@
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="3"/>
-      <c r="B148" s="3"/>
       <c r="C148" s="3"/>
       <c r="D148" s="3"/>
       <c r="E148" s="3"/>
@@ -7553,7 +7970,6 @@
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="3"/>
-      <c r="B149" s="3"/>
       <c r="C149" s="3"/>
       <c r="D149" s="3"/>
       <c r="E149" s="3"/>
@@ -7568,7 +7984,6 @@
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="3"/>
-      <c r="B150" s="3"/>
       <c r="C150" s="3"/>
       <c r="D150" s="3"/>
       <c r="E150" s="3"/>
@@ -7583,7 +7998,6 @@
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="3"/>
-      <c r="B151" s="3"/>
       <c r="C151" s="3"/>
       <c r="D151" s="3"/>
       <c r="E151" s="3"/>
@@ -7598,7 +8012,6 @@
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="3"/>
-      <c r="B152" s="3"/>
       <c r="C152" s="3"/>
       <c r="D152" s="3"/>
       <c r="E152" s="3"/>
@@ -7613,7 +8026,6 @@
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="3"/>
-      <c r="B153" s="3"/>
       <c r="C153" s="3"/>
       <c r="D153" s="3"/>
       <c r="E153" s="3"/>
@@ -7628,7 +8040,6 @@
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="3"/>
-      <c r="B154" s="3"/>
       <c r="C154" s="3"/>
       <c r="D154" s="3"/>
       <c r="E154" s="3"/>
@@ -7643,7 +8054,6 @@
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="3"/>
-      <c r="B155" s="3"/>
       <c r="C155" s="3"/>
       <c r="D155" s="3"/>
       <c r="E155" s="3"/>
@@ -7658,7 +8068,6 @@
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="3"/>
-      <c r="B156" s="3"/>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
       <c r="E156" s="3"/>
@@ -7673,7 +8082,6 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3"/>
@@ -7688,7 +8096,6 @@
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
       <c r="C158" s="3"/>
       <c r="D158" s="3"/>
       <c r="E158" s="3"/>
@@ -7703,7 +8110,6 @@
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
       <c r="C159" s="3"/>
       <c r="D159" s="3"/>
       <c r="E159" s="3"/>
@@ -7718,7 +8124,6 @@
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3"/>
@@ -7733,7 +8138,6 @@
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3"/>
@@ -7748,7 +8152,6 @@
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="3"/>
-      <c r="B162" s="3"/>
       <c r="C162" s="3"/>
       <c r="D162" s="3"/>
       <c r="E162" s="3"/>
@@ -7763,7 +8166,6 @@
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="3"/>
-      <c r="B163" s="3"/>
       <c r="C163" s="3"/>
       <c r="D163" s="3"/>
       <c r="E163" s="3"/>
@@ -7778,7 +8180,6 @@
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
       <c r="C164" s="3"/>
       <c r="D164" s="3"/>
       <c r="E164" s="3"/>
@@ -7793,7 +8194,6 @@
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
       <c r="C165" s="3"/>
       <c r="D165" s="3"/>
       <c r="E165" s="3"/>
@@ -7808,7 +8208,6 @@
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="3"/>
-      <c r="B166" s="3"/>
       <c r="C166" s="3"/>
       <c r="D166" s="3"/>
       <c r="E166" s="3"/>
@@ -7823,7 +8222,6 @@
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="3"/>
-      <c r="B167" s="3"/>
       <c r="C167" s="3"/>
       <c r="D167" s="3"/>
       <c r="E167" s="3"/>
@@ -7838,7 +8236,6 @@
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
       <c r="C168" s="3"/>
       <c r="D168" s="3"/>
       <c r="E168" s="3"/>
@@ -7853,7 +8250,6 @@
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="3"/>
-      <c r="B169" s="3"/>
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3"/>
@@ -7868,7 +8264,6 @@
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="3"/>
-      <c r="B170" s="3"/>
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3"/>
@@ -7883,7 +8278,6 @@
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="3"/>
-      <c r="B171" s="3"/>
       <c r="C171" s="3"/>
       <c r="D171" s="3"/>
       <c r="E171" s="3"/>
@@ -7898,7 +8292,6 @@
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="3"/>
-      <c r="B172" s="3"/>
       <c r="C172" s="3"/>
       <c r="D172" s="3"/>
       <c r="E172" s="3"/>
@@ -7913,7 +8306,6 @@
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="3"/>
-      <c r="B173" s="3"/>
       <c r="C173" s="3"/>
       <c r="D173" s="3"/>
       <c r="E173" s="3"/>
@@ -7928,7 +8320,6 @@
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="3"/>
-      <c r="B174" s="3"/>
       <c r="C174" s="3"/>
       <c r="D174" s="3"/>
       <c r="E174" s="3"/>
@@ -7943,7 +8334,6 @@
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="3"/>
-      <c r="B175" s="3"/>
       <c r="C175" s="3"/>
       <c r="D175" s="3"/>
       <c r="E175" s="3"/>
@@ -7958,7 +8348,6 @@
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="3"/>
-      <c r="B176" s="3"/>
       <c r="C176" s="3"/>
       <c r="D176" s="3"/>
       <c r="E176" s="3"/>
@@ -7973,7 +8362,6 @@
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="3"/>
-      <c r="B177" s="3"/>
       <c r="C177" s="3"/>
       <c r="D177" s="3"/>
       <c r="E177" s="3"/>
@@ -7988,7 +8376,6 @@
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="3"/>
-      <c r="B178" s="3"/>
       <c r="C178" s="3"/>
       <c r="D178" s="3"/>
       <c r="E178" s="3"/>
@@ -8003,7 +8390,6 @@
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="3"/>
-      <c r="B179" s="3"/>
       <c r="C179" s="3"/>
       <c r="D179" s="3"/>
       <c r="E179" s="3"/>
@@ -8018,7 +8404,6 @@
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="3"/>
-      <c r="B180" s="3"/>
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3"/>
@@ -8033,7 +8418,6 @@
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="3"/>
-      <c r="B181" s="3"/>
       <c r="C181" s="3"/>
       <c r="D181" s="3"/>
       <c r="E181" s="3"/>
@@ -8048,7 +8432,6 @@
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="3"/>
-      <c r="B182" s="3"/>
       <c r="C182" s="3"/>
       <c r="D182" s="3"/>
       <c r="E182" s="3"/>
@@ -8063,7 +8446,6 @@
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="3"/>
-      <c r="B183" s="3"/>
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3"/>
@@ -8078,7 +8460,6 @@
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="3"/>
-      <c r="B184" s="3"/>
       <c r="C184" s="3"/>
       <c r="D184" s="3"/>
       <c r="E184" s="3"/>
@@ -8093,7 +8474,6 @@
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="3"/>
-      <c r="B185" s="3"/>
       <c r="C185" s="3"/>
       <c r="D185" s="3"/>
       <c r="E185" s="3"/>
@@ -8108,7 +8488,6 @@
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="3"/>
-      <c r="B186" s="3"/>
       <c r="C186" s="3"/>
       <c r="D186" s="3"/>
       <c r="E186" s="3"/>
@@ -8123,7 +8502,6 @@
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="3"/>
-      <c r="B187" s="3"/>
       <c r="C187" s="3"/>
       <c r="D187" s="3"/>
       <c r="E187" s="3"/>
@@ -8138,7 +8516,6 @@
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="3"/>
-      <c r="B188" s="3"/>
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3"/>
@@ -8153,7 +8530,6 @@
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="3"/>
-      <c r="B189" s="3"/>
       <c r="C189" s="3"/>
       <c r="D189" s="3"/>
       <c r="E189" s="3"/>
@@ -8168,7 +8544,6 @@
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="3"/>
-      <c r="B190" s="3"/>
       <c r="C190" s="3"/>
       <c r="D190" s="3"/>
       <c r="E190" s="3"/>
@@ -8183,7 +8558,6 @@
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="3"/>
-      <c r="B191" s="3"/>
       <c r="C191" s="3"/>
       <c r="D191" s="3"/>
       <c r="E191" s="3"/>
@@ -8198,7 +8572,6 @@
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="3"/>
-      <c r="B192" s="3"/>
       <c r="C192" s="3"/>
       <c r="D192" s="3"/>
       <c r="E192" s="3"/>
@@ -8213,7 +8586,6 @@
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="3"/>
-      <c r="B193" s="3"/>
       <c r="C193" s="3"/>
       <c r="D193" s="3"/>
       <c r="E193" s="3"/>
@@ -8228,7 +8600,6 @@
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="3"/>
-      <c r="B194" s="3"/>
       <c r="C194" s="3"/>
       <c r="D194" s="3"/>
       <c r="E194" s="3"/>
@@ -8243,7 +8614,6 @@
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="3"/>
-      <c r="B195" s="3"/>
       <c r="C195" s="3"/>
       <c r="D195" s="3"/>
       <c r="E195" s="3"/>
@@ -8258,7 +8628,6 @@
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="3"/>
-      <c r="B196" s="3"/>
       <c r="C196" s="3"/>
       <c r="D196" s="3"/>
       <c r="E196" s="3"/>
@@ -8273,7 +8642,6 @@
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="3"/>
-      <c r="B197" s="3"/>
       <c r="C197" s="3"/>
       <c r="D197" s="3"/>
       <c r="E197" s="3"/>
@@ -8288,7 +8656,6 @@
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="3"/>
-      <c r="B198" s="3"/>
       <c r="C198" s="3"/>
       <c r="D198" s="3"/>
       <c r="E198" s="3"/>
@@ -8303,7 +8670,6 @@
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="3"/>
-      <c r="B199" s="3"/>
       <c r="C199" s="3"/>
       <c r="D199" s="3"/>
       <c r="E199" s="3"/>
@@ -8318,7 +8684,6 @@
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="3"/>
-      <c r="B200" s="3"/>
       <c r="C200" s="3"/>
       <c r="D200" s="3"/>
       <c r="E200" s="3"/>
@@ -8364,7 +8729,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H200"/>
+  <dimension ref="A1:M200"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="24" customWidth="1"/>
@@ -8373,177 +8738,260 @@
     <col min="8" max="8" width="36" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="15">
+    <row r="1" spans="1:13" ht="15">
       <c r="A1" s="5" t="s">
-        <v>198</v>
+        <v>151</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>199</v>
+        <v>152</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>200</v>
+        <v>153</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="28.5">
+      <c r="I1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K1" t="s">
+        <v>326</v>
+      </c>
+      <c r="L1" t="s">
+        <v>327</v>
+      </c>
+      <c r="M1" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="28.5">
       <c r="A2" s="3" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8" ht="28.5">
+    <row r="3" spans="1:13" ht="28.5">
       <c r="A3" s="3" t="s">
-        <v>208</v>
+        <v>161</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>209</v>
+        <v>162</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>210</v>
+        <v>163</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>211</v>
+        <v>164</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>212</v>
+        <v>165</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8" ht="28.5">
+    <row r="4" spans="1:13" ht="28.5">
       <c r="A4" s="3" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>215</v>
+        <v>302</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>216</v>
+        <v>303</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>56</v>
+        <v>304</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H4" s="3"/>
-    </row>
-    <row r="5" spans="1:8" ht="28.5">
+        <v>305</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="I4" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" t="s">
+        <v>51</v>
+      </c>
+      <c r="K4" t="s">
+        <v>306</v>
+      </c>
+      <c r="L4" t="s">
+        <v>75</v>
+      </c>
+      <c r="M4" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28.5">
       <c r="A5" s="3" t="s">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>219</v>
+        <v>308</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>220</v>
+        <v>309</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H5" s="3"/>
-    </row>
-    <row r="6" spans="1:8" ht="28.5">
+      <c r="I5" t="s">
+        <v>52</v>
+      </c>
+      <c r="J5" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" t="s">
+        <v>97</v>
+      </c>
+      <c r="L5" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="28.5">
       <c r="A6" s="3" t="s">
-        <v>221</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>222</v>
+        <v>234</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>223</v>
+        <v>313</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>225</v>
+        <v>314</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>56</v>
+        <v>315</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H6" s="3"/>
-    </row>
-    <row r="7" spans="1:8" ht="28.5">
+        <v>316</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" t="s">
+        <v>51</v>
+      </c>
+      <c r="K6" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" t="s">
+        <v>317</v>
+      </c>
+      <c r="M6" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28.5">
       <c r="A7" s="3" t="s">
-        <v>226</v>
+        <v>319</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>228</v>
+        <v>320</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>229</v>
+        <v>281</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>230</v>
+        <v>268</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>56</v>
+        <v>321</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="H7" s="3"/>
-    </row>
-    <row r="8" spans="1:8">
+        <v>322</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I7" t="s">
+        <v>52</v>
+      </c>
+      <c r="J7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7" t="s">
+        <v>269</v>
+      </c>
+      <c r="M7" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="3"/>
@@ -8553,7 +9001,7 @@
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:13">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="3"/>
@@ -8563,7 +9011,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:13">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="3"/>
@@ -8573,7 +9021,7 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:13">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
@@ -8583,7 +9031,7 @@
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:13">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="3"/>
@@ -8593,7 +9041,7 @@
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:13">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -8603,7 +9051,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:13">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="3"/>
@@ -8613,7 +9061,7 @@
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:13">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="3"/>
@@ -8623,7 +9071,7 @@
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:13">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
@@ -10474,6 +10922,7 @@
       <c r="H200" s="3"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <conditionalFormatting sqref="F2:F200">
     <cfRule type="expression" dxfId="5" priority="1">
       <formula>$F2="Blocked"</formula>
@@ -10517,40 +10966,40 @@
   <sheetData>
     <row r="1" spans="1:13" ht="15">
       <c r="A1" s="5" t="s">
-        <v>231</v>
+        <v>167</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>232</v>
+        <v>168</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>233</v>
+        <v>169</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>234</v>
+        <v>170</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>6</v>
@@ -10558,188 +11007,188 @@
     </row>
     <row r="2" spans="1:13" ht="28.5">
       <c r="A2" s="3" t="s">
-        <v>238</v>
+        <v>174</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>239</v>
+        <v>175</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>240</v>
+        <v>176</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>241</v>
+        <v>177</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>242</v>
+        <v>178</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>243</v>
+        <v>179</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>244</v>
+        <v>180</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>245</v>
+        <v>181</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="M2" s="3"/>
     </row>
     <row r="3" spans="1:13" ht="28.5">
       <c r="A3" s="3" t="s">
-        <v>246</v>
+        <v>182</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>247</v>
+        <v>183</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>248</v>
+        <v>184</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>249</v>
+        <v>185</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>250</v>
+        <v>186</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>251</v>
+        <v>187</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3" t="s">
-        <v>252</v>
+        <v>188</v>
       </c>
       <c r="M3" s="3"/>
     </row>
     <row r="4" spans="1:13" ht="28.5">
       <c r="A4" s="3" t="s">
-        <v>253</v>
+        <v>189</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>254</v>
+        <v>190</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>255</v>
+        <v>191</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>257</v>
+        <v>193</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>258</v>
+        <v>194</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="M4" s="3"/>
     </row>
     <row r="5" spans="1:13" ht="42.75">
       <c r="A5" s="3" t="s">
-        <v>259</v>
+        <v>195</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>261</v>
+        <v>197</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>263</v>
+        <v>199</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>264</v>
+        <v>200</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>265</v>
+        <v>201</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="M5" s="3"/>
     </row>
     <row r="6" spans="1:13" ht="57">
       <c r="A6" s="3" t="s">
-        <v>266</v>
+        <v>202</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>260</v>
+        <v>196</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>267</v>
+        <v>203</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>268</v>
+        <v>204</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>263</v>
+        <v>199</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>269</v>
+        <v>205</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>270</v>
+        <v>206</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="M6" s="3"/>
     </row>
@@ -13700,84 +14149,84 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>207</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>272</v>
+        <v>208</v>
       </c>
       <c r="B4" t="s">
-        <v>273</v>
+        <v>209</v>
       </c>
       <c r="C4" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="D4" t="s">
-        <v>274</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="B5" t="s">
-        <v>276</v>
+        <v>212</v>
       </c>
       <c r="D5" t="s">
-        <v>277</v>
+        <v>213</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>278</v>
+        <v>214</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" t="s">
-        <v>279</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/docs/standards/SJTDM_TAZ_Migration_Project_Control.xlsx
+++ b/docs/standards/SJTDM_TAZ_Migration_Project_Control.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Kschellinger\SJTPO_Git\SJTDM_TAZ_Migration\docs\standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E9025B6-D93D-495D-88BB-DF702857C25D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF78DE4B-6FA1-4EA9-B0FB-2AD7A5D2E0DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1500" yWindow="930" windowWidth="29010" windowHeight="14370" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="810" windowWidth="29010" windowHeight="14370" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="331">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="602" uniqueCount="336">
   <si>
     <t>SJTDM TAZ Migration and Data Validation – Project Control Workbook</t>
   </si>
@@ -1028,10 +1028,25 @@
     <t>Column5</t>
   </si>
   <si>
-    <t>Core project objective.  First-pass review of recreational model TAZs completed. TAZs containing significant recreational land-use patterns and sub-census-block characteristics identified. Findings indicate that preservation of model-relevant land-use geography is more important than geometric similarity between legacy and proposed TAZ boundaries.</t>
-  </si>
-  <si>
     <t>Recreational model screening methodology tested. Initial review confirms geometry-only comparisons are insufficient for evaluating migration quality. QA/QC framework shall evaluate preservation of socioeconomic and recreational model characteristics in addition to geometric correspondence.</t>
+  </si>
+  <si>
+    <t>Core project objective.  First-pass review of recreational model TAZs completed. A first-pass review of all 534 recreational model TAZs was completed. A total of 169 TAZs (31.6%) were identified as containing significant sub-census-block characteristics and were exported to REC_MODEL_SUB_Y for further evaluation. Impact assessment determined that only 45 TAZs (8.4%) exhibited Moderate or High potential effects on demographic allocation under a pure 2020 Census Block methodology. The remaining 489 TAZs (91.6%) exhibited Low or No Significant impact.</t>
+  </si>
+  <si>
+    <t>DI-009</t>
+  </si>
+  <si>
+    <t>REC_MODEL_SUB_Y_20260615</t>
+  </si>
+  <si>
+    <t>\\sjtpo-fs.sjtpo.org\users$\Kschellinger\My Documents\ArcGIS\Projects\SJTDM_TAZ_Master\SJTDM_2020.gdb</t>
+  </si>
+  <si>
+    <t>Geodatabase</t>
+  </si>
+  <si>
+    <t>C:\Users\Kschellinger\SJTPO_Git\SJTDM_TAZ_Migration\data\derived\REC_MODEL_SUB_Y.shp</t>
   </si>
 </sst>
 </file>
@@ -2155,7 +2170,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="185.25">
+    <row r="13" spans="1:13" ht="299.25">
       <c r="A13" s="10" t="s">
         <v>226</v>
       </c>
@@ -2189,7 +2204,7 @@
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="142.5">
@@ -2226,7 +2241,7 @@
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="28.5">
@@ -6022,14 +6037,27 @@
         <v>292</v>
       </c>
     </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
+    <row r="10" spans="1:13" ht="69.75" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="B10" t="s">
+        <v>332</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>335</v>
+      </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="H10" s="3">
+        <v>2020</v>
+      </c>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
